--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92564334265</v>
+        <v>46157.93084626782</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93084626782</v>
+        <v>46157.93162804798</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93162804798</v>
+        <v>46157.93396450739</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93396450739</v>
+        <v>46157.93713760511</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93713760511</v>
+        <v>46158.28212887779</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28212887779</v>
+        <v>46158.29674094189</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29674094189</v>
+        <v>46158.29810423672</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29810423672</v>
+        <v>46158.33383776449</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33383776449</v>
+        <v>46158.36852268261</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36852268261</v>
+        <v>46158.37283923075</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
